--- a/tools/importer/reports/import-carousel-landing-page.report.xlsx
+++ b/tools/importer/reports/import-carousel-landing-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="243">
   <si>
     <t>_reportFile</t>
   </si>
@@ -103,7 +103,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-09-12T11:04:22.829Z</t>
+    <t>2026-09-13T15:46:34.449Z</t>
   </si>
   <si>
     <t>University of Nottingham</t>
@@ -112,6 +112,21 @@
     <t>https://www.nottingham.ac.uk/</t>
   </si>
   <si>
+    <t>pgstudy.report.json</t>
+  </si>
+  <si>
+    <t>pgstudy</t>
+  </si>
+  <si>
+    <t>2026-09-13T15:48:46.510Z</t>
+  </si>
+  <si>
+    <t>Postgraduate study</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/pgstudy/</t>
+  </si>
+  <si>
     <t>aau/goals.aspx.report.json</t>
   </si>
   <si>
@@ -370,6 +385,105 @@
     <t>https://www.nottingham.ac.uk/app/objectives.aspx</t>
   </si>
   <si>
+    <t>open-days/undergraduate-open-days.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-2"]</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days</t>
+  </si>
+  <si>
+    <t>hero-cards-landing-2</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:59:39.821Z</t>
+  </si>
+  <si>
+    <t>Book your place</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/open-days/undergraduate-open-days/index.aspx</t>
+  </si>
+  <si>
+    <t>studywithus/international-applicants.report.json</t>
+  </si>
+  <si>
+    <t>studywithus/international-applicants</t>
+  </si>
+  <si>
+    <t>2026-09-13T15:48:56.004Z</t>
+  </si>
+  <si>
+    <t>Information for international applicants</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/studywithus/international-applicants/index.aspx</t>
+  </si>
+  <si>
+    <t>studywithus/study-with-us.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-2","search-course-light","cards-minimal-dark-withimg-5","cards-minimal-dark-withimg-5","cards-ranking-gold","cards-promo-dark"]</t>
+  </si>
+  <si>
+    <t>studywithus/study-with-us</t>
+  </si>
+  <si>
+    <t>minimal-content-page-4</t>
+  </si>
+  <si>
+    <t>2026-09-13T15:40:42.088Z</t>
+  </si>
+  <si>
+    <t>Study with us | University of Nottingham</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/studywithus/study-with-us.aspx</t>
+  </si>
+  <si>
+    <t>ugstudy/visitingus.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-2","cards-minimal-dark-withimg-5","cards-minimal-dark-withimg-5","cards-minimal-dark-withimg-5","cards-minimal-dark-withimg-5","columns-minimal-dark-withimg-2"]</t>
+  </si>
+  <si>
+    <t>ugstudy/visitingus</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:29:33.513Z</t>
+  </si>
+  <si>
+    <t>Campus and visits</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/ugstudy/visitingus/</t>
+  </si>
+  <si>
+    <t>virtual/chat.aspx.report.json</t>
+  </si>
+  <si>
+    <t>virtual/chat.aspx</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:57:15.167Z</t>
+  </si>
+  <si>
+    <t>Contact us</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/virtual/chat.aspx</t>
+  </si>
+  <si>
+    <t>virtual/chat.report.json</t>
+  </si>
+  <si>
+    <t>virtual/chat</t>
+  </si>
+  <si>
+    <t>2026-09-13T12:00:12.827Z</t>
+  </si>
+  <si>
     <t>aau/news-events/index.aspx.report.json</t>
   </si>
   <si>
@@ -410,6 +524,222 @@
   </si>
   <si>
     <t>https://www.nottingham.ac.uk/aau/news-events/projects.aspx</t>
+  </si>
+  <si>
+    <t>isac/news-items/studying-tumour-metabolism-from-every-angle.aspx.report.json</t>
+  </si>
+  <si>
+    <t>isac/news-items/studying-tumour-metabolism-from-every-angle.aspx</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:56:13.767Z</t>
+  </si>
+  <si>
+    <t>Rosetta | Cancer Grand Challenges</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/isac/news-items/studying-tumour-metabolism-from-every-angle.aspx</t>
+  </si>
+  <si>
+    <t>isac/news-items/studying-tumour-metabolism-from-every-angle.report.json</t>
+  </si>
+  <si>
+    <t>isac/news-items/studying-tumour-metabolism-from-every-angle</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:59:14.855Z</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/frequently-asked-questions.aspx.report.json</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/frequently-asked-questions.aspx</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:56:22.057Z</t>
+  </si>
+  <si>
+    <t>Frequently asked questions</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/open-days/undergraduate-open-days/frequently-asked-questions.aspx</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/frequently-asked-questions.report.json</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/frequently-asked-questions</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:59:22.607Z</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/index.aspx.report.json</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/index.aspx</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:56:37.545Z</t>
+  </si>
+  <si>
+    <t>studywithus/international-applicants/index.aspx.report.json</t>
+  </si>
+  <si>
+    <t>studywithus/international-applicants/index.aspx</t>
+  </si>
+  <si>
+    <t>2026-09-13T15:47:53.693Z</t>
+  </si>
+  <si>
+    <t>studywithus/ugstudy/find-uon.report.json</t>
+  </si>
+  <si>
+    <t>["columns-minimal-dark-withimg-2","columns-minimal-dark-withimg-2"]</t>
+  </si>
+  <si>
+    <t>studywithus/ugstudy/find-uon</t>
+  </si>
+  <si>
+    <t>2026-09-13T15:47:35.836Z</t>
+  </si>
+  <si>
+    <t>Find your course</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/studywithus/ugstudy/find-uon.html</t>
+  </si>
+  <si>
+    <t>studywithus/what-next/fees-and-funding.report.json</t>
+  </si>
+  <si>
+    <t>studywithus/what-next/fees-and-funding</t>
+  </si>
+  <si>
+    <t>rich-text-page</t>
+  </si>
+  <si>
+    <t>2026-09-13T15:45:26.625Z</t>
+  </si>
+  <si>
+    <t>Fees and funding - The University of Nottingham</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/studywithus/what-next/fees-and-funding.aspx</t>
+  </si>
+  <si>
+    <t>ugstudy/visitingus/visitingus.aspx.report.json</t>
+  </si>
+  <si>
+    <t>ugstudy/visitingus/visitingus.aspx</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:57:06.274Z</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/ugstudy/visitingus/visitingus.aspx</t>
+  </si>
+  <si>
+    <t>ugstudy/visitingus/visitingus.report.json</t>
+  </si>
+  <si>
+    <t>ugstudy/visitingus/visitingus</t>
+  </si>
+  <si>
+    <t>2026-09-13T12:00:04.542Z</t>
+  </si>
+  <si>
+    <t>workingwithbusiness/degree-apprenticeships/degree-apprenticeships.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-hero-dark","cards-nav-light","cards-icon-light","columns-video-light","cards-promo-dark","cards-promo-dark","cards-promo-dark","cards-minimal-dark-withimg-5"]</t>
+  </si>
+  <si>
+    <t>workingwithbusiness/degree-apprenticeships/degree-apprenticeships</t>
+  </si>
+  <si>
+    <t>degree-apprenticeships</t>
+  </si>
+  <si>
+    <t>2026-09-13T15:44:23.908Z</t>
+  </si>
+  <si>
+    <t>Degree Apprenticeships - The University of Nottingham</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/workingwithbusiness/degree-apprenticeships/degree-apprenticeships.aspx</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/getting-here/getting-here.aspx.report.json</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/getting-here/getting-here.aspx</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:56:29.319Z</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/open-days/undergraduate-open-days/getting-here/getting-here.aspx</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/getting-here/getting-here.report.json</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/getting-here/getting-here</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:59:31.587Z</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/plan-your-day/accessibility-and-inclusivity.aspx.report.json</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/plan-your-day/accessibility-and-inclusivity.aspx</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:56:45.926Z</t>
+  </si>
+  <si>
+    <t>Accessibility and inclusivity</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/open-days/undergraduate-open-days/plan-your-day/accessibility-and-inclusivity.aspx</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/plan-your-day/accessibility-and-inclusivity.report.json</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/plan-your-day/accessibility-and-inclusivity</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:59:47.906Z</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/plan-your-day/plan-your-day.aspx.report.json</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/plan-your-day/plan-your-day.aspx</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:56:59.800Z</t>
+  </si>
+  <si>
+    <t>Plan your day</t>
+  </si>
+  <si>
+    <t>https://www.nottingham.ac.uk/open-days/undergraduate-open-days/plan-your-day/plan-your-day.aspx</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/plan-your-day/plan-your-day.report.json</t>
+  </si>
+  <si>
+    <t>open-days/undergraduate-open-days/plan-your-day/plan-your-day</t>
+  </si>
+  <si>
+    <t>2026-09-13T11:59:57.059Z</t>
   </si>
 </sst>
 </file>
@@ -798,11 +1128,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
@@ -1009,21 +1339,21 @@
         <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -1032,10 +1362,10 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
         <v>51</v>
@@ -1046,7 +1376,7 @@
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
         <v>53</v>
@@ -1061,21 +1391,21 @@
         <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1084,24 +1414,24 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
         <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1110,24 +1440,24 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1136,24 +1466,24 @@
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1162,24 +1492,24 @@
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
         <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1188,24 +1518,24 @@
         <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1214,24 +1544,24 @@
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1240,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="H17" t="s">
         <v>84</v>
@@ -1254,7 +1584,7 @@
         <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
         <v>86</v>
@@ -1321,21 +1651,21 @@
         <v>97</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="H20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1344,10 +1674,10 @@
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G21" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s">
         <v>103</v>
@@ -1451,62 +1781,686 @@
         <v>121</v>
       </c>
       <c r="G25" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="H25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="F26" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G26" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H26" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G27" t="s">
+        <v>134</v>
+      </c>
+      <c r="H27" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" t="s">
+        <v>141</v>
+      </c>
+      <c r="H28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" t="s">
+        <v>146</v>
+      </c>
+      <c r="G29" t="s">
+        <v>147</v>
+      </c>
+      <c r="H29" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" t="s">
+        <v>151</v>
+      </c>
+      <c r="G30" t="s">
+        <v>152</v>
+      </c>
+      <c r="H30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" t="s">
+        <v>156</v>
+      </c>
+      <c r="G31" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>163</v>
+      </c>
+      <c r="G33" t="s">
+        <v>164</v>
+      </c>
+      <c r="H33" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>168</v>
+      </c>
+      <c r="G34" t="s">
+        <v>169</v>
+      </c>
+      <c r="H34" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>171</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" t="s">
+        <v>173</v>
+      </c>
+      <c r="G35" t="s">
+        <v>174</v>
+      </c>
+      <c r="H35" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>127</v>
+      </c>
+      <c r="F36" t="s">
+        <v>178</v>
+      </c>
+      <c r="G36" t="s">
+        <v>174</v>
+      </c>
+      <c r="H36" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>179</v>
+      </c>
+      <c r="B37" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" t="s">
+        <v>180</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>127</v>
+      </c>
+      <c r="F37" t="s">
+        <v>181</v>
+      </c>
+      <c r="G37" t="s">
+        <v>182</v>
+      </c>
+      <c r="H37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" t="s">
+        <v>186</v>
+      </c>
+      <c r="G38" t="s">
+        <v>182</v>
+      </c>
+      <c r="H38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>187</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s">
+        <v>188</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>127</v>
+      </c>
+      <c r="F39" t="s">
+        <v>189</v>
+      </c>
+      <c r="G39" t="s">
         <v>129</v>
       </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="H39" t="s">
         <v>130</v>
       </c>
-      <c r="G27" t="s">
-        <v>131</v>
-      </c>
-      <c r="H27" t="s">
-        <v>132</v>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>190</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>192</v>
+      </c>
+      <c r="G40" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" t="s">
+        <v>196</v>
+      </c>
+      <c r="G41" t="s">
+        <v>197</v>
+      </c>
+      <c r="H41" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>199</v>
+      </c>
+      <c r="B42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" t="s">
+        <v>200</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>201</v>
+      </c>
+      <c r="F42" t="s">
+        <v>202</v>
+      </c>
+      <c r="G42" t="s">
+        <v>203</v>
+      </c>
+      <c r="H42" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" t="s">
+        <v>206</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>127</v>
+      </c>
+      <c r="F43" t="s">
+        <v>207</v>
+      </c>
+      <c r="G43" t="s">
+        <v>147</v>
+      </c>
+      <c r="H43" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>209</v>
+      </c>
+      <c r="B44" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" t="s">
+        <v>210</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>127</v>
+      </c>
+      <c r="F44" t="s">
+        <v>211</v>
+      </c>
+      <c r="G44" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>215</v>
+      </c>
+      <c r="F45" t="s">
+        <v>216</v>
+      </c>
+      <c r="G45" t="s">
+        <v>217</v>
+      </c>
+      <c r="H45" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>219</v>
+      </c>
+      <c r="B46" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" t="s">
+        <v>220</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>127</v>
+      </c>
+      <c r="F46" t="s">
+        <v>221</v>
+      </c>
+      <c r="G46" t="s">
+        <v>222</v>
+      </c>
+      <c r="H46" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>224</v>
+      </c>
+      <c r="B47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" t="s">
+        <v>225</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>127</v>
+      </c>
+      <c r="F47" t="s">
+        <v>226</v>
+      </c>
+      <c r="G47" t="s">
+        <v>222</v>
+      </c>
+      <c r="H47" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>227</v>
+      </c>
+      <c r="B48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" t="s">
+        <v>228</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>127</v>
+      </c>
+      <c r="F48" t="s">
+        <v>229</v>
+      </c>
+      <c r="G48" t="s">
+        <v>230</v>
+      </c>
+      <c r="H48" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>232</v>
+      </c>
+      <c r="B49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" t="s">
+        <v>233</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>127</v>
+      </c>
+      <c r="F49" t="s">
+        <v>234</v>
+      </c>
+      <c r="G49" t="s">
+        <v>230</v>
+      </c>
+      <c r="H49" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>235</v>
+      </c>
+      <c r="B50" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" t="s">
+        <v>236</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>127</v>
+      </c>
+      <c r="F50" t="s">
+        <v>237</v>
+      </c>
+      <c r="G50" t="s">
+        <v>238</v>
+      </c>
+      <c r="H50" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>240</v>
+      </c>
+      <c r="B51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" t="s">
+        <v>241</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>127</v>
+      </c>
+      <c r="F51" t="s">
+        <v>242</v>
+      </c>
+      <c r="G51" t="s">
+        <v>238</v>
+      </c>
+      <c r="H51" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
